--- a/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-53,14; -18,74</t>
+          <t>-55,43; -19,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-73,69; -32,85</t>
+          <t>-71,78; -30,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-64,48; -34,26</t>
+          <t>-65,83; -34,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -16,22</t>
+          <t>-49,54; -16,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,21; -27,97</t>
+          <t>-67,49; -28,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -28,94</t>
+          <t>-60,54; -26,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,57; -21,45</t>
+          <t>-45,29; -21,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,15; -36,09</t>
+          <t>-63,74; -36,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-57,74; -35,27</t>
+          <t>-59,26; -34,96</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,14; -18,74</t>
+          <t>-55,43; -19,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,69; -32,85</t>
+          <t>-71,78; -30,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,48; -34,26</t>
+          <t>-65,83; -34,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -16,22</t>
+          <t>-49,54; -16,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,21; -27,97</t>
+          <t>-67,49; -28,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,73; -28,94</t>
+          <t>-60,54; -26,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,57; -21,45</t>
+          <t>-45,29; -21,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,15; -36,09</t>
+          <t>-63,74; -36,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,74; -35,27</t>
+          <t>-59,26; -34,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -12,28</t>
+          <t>-41,27; -11,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-58,92; -15,25</t>
+          <t>-58,66; -15,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -20,33</t>
+          <t>-53,66; -21,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-64,3; -17,33</t>
+          <t>-64,98; -17,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,97; -17,47</t>
+          <t>-55,37; -18,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,12; -15,0</t>
+          <t>-46,93; -15,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -18,84</t>
+          <t>-42,53; -17,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,79; -21,94</t>
+          <t>-50,29; -21,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-46,13; -21,57</t>
+          <t>-45,81; -21,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -12,28</t>
+          <t>-41,27; -11,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,92; -15,25</t>
+          <t>-58,66; -15,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -20,33</t>
+          <t>-53,66; -21,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,3; -17,33</t>
+          <t>-64,98; -17,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,97; -17,47</t>
+          <t>-55,37; -18,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,12; -15,0</t>
+          <t>-46,93; -15,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,82; -18,84</t>
+          <t>-42,53; -17,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,79; -21,94</t>
+          <t>-50,29; -21,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,13; -21,57</t>
+          <t>-45,81; -21,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-42,35; -5,47</t>
+          <t>-41,76; -5,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -6,9</t>
+          <t>-57,44; -8,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-73,15; -22,17</t>
+          <t>-68,83; -21,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,16; -5,92</t>
+          <t>-45,63; -5,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,52; -18,83</t>
+          <t>-75,1; -23,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -29,44</t>
+          <t>-70,39; -28,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,14; -9,15</t>
+          <t>-36,74; -8,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,24; -21,76</t>
+          <t>-54,48; -19,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-66,33; -33,29</t>
+          <t>-66,47; -32,21</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,35; -5,47</t>
+          <t>-41,76; -5,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -6,9</t>
+          <t>-57,44; -8,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,15; -22,17</t>
+          <t>-68,83; -21,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,16; -5,92</t>
+          <t>-45,63; -5,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,52; -18,83</t>
+          <t>-75,1; -23,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,1; -29,44</t>
+          <t>-70,39; -28,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,14; -9,15</t>
+          <t>-36,74; -8,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; -21,76</t>
+          <t>-54,48; -19,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,33; -33,29</t>
+          <t>-66,47; -32,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -32,14</t>
+          <t>-54,13; -30,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -28,57</t>
+          <t>-51,32; -28,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,3; -11,42</t>
+          <t>-61,31; -12,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-54,29; -32,62</t>
+          <t>-54,88; -33,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,06; -40,98</t>
+          <t>-68,01; -41,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,32; -27,51</t>
+          <t>-53,86; -27,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,26; -35,62</t>
+          <t>-50,63; -34,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-53,9; -36,38</t>
+          <t>-54,83; -37,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -17,86</t>
+          <t>-51,07; -18,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,87; -32,14</t>
+          <t>-54,13; -30,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -28,57</t>
+          <t>-51,32; -28,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,3; -11,42</t>
+          <t>-61,31; -12,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,29; -32,62</t>
+          <t>-54,88; -33,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,06; -40,98</t>
+          <t>-68,01; -41,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,32; -27,51</t>
+          <t>-53,86; -27,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,26; -35,62</t>
+          <t>-50,63; -34,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,9; -36,38</t>
+          <t>-54,83; -37,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-49,94; -17,86</t>
+          <t>-51,07; -18,04</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-48,89; -20,53</t>
+          <t>-48,33; -19,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-57,9; -24,84</t>
+          <t>-59,02; -26,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -30,03</t>
+          <t>-59,47; -29,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -20,39</t>
+          <t>-46,77; -18,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,54; -19,88</t>
+          <t>-50,7; -19,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -28,65</t>
+          <t>-56,82; -29,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -23,31</t>
+          <t>-43,99; -22,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -25,37</t>
+          <t>-49,0; -26,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-53,22; -32,69</t>
+          <t>-54,11; -33,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,89; -20,53</t>
+          <t>-48,33; -19,5</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,9; -24,84</t>
+          <t>-59,02; -26,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -30,03</t>
+          <t>-59,47; -29,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -20,39</t>
+          <t>-46,77; -18,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,54; -19,88</t>
+          <t>-50,7; -19,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,13; -28,65</t>
+          <t>-56,82; -29,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,91; -23,31</t>
+          <t>-43,99; -22,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -25,37</t>
+          <t>-49,0; -26,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-53,22; -32,69</t>
+          <t>-54,11; -33,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-70,06; -9,25</t>
+          <t>-69,12; -9,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-55,19; -13,59</t>
+          <t>-53,51; -11,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-78,04; -32,28</t>
+          <t>-78,21; -30,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-64,27; -20,06</t>
+          <t>-65,97; -21,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -32,2</t>
+          <t>-81,53; -31,19</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-73,8; -25,62</t>
+          <t>-74,81; -27,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -21,66</t>
+          <t>-54,68; -20,69</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-61,13; -27,09</t>
+          <t>-58,86; -26,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-70,06; -35,72</t>
+          <t>-68,14; -36,41</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-70,06; -9,25</t>
+          <t>-69,12; -9,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-55,19; -13,59</t>
+          <t>-53,51; -11,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,04; -32,28</t>
+          <t>-78,21; -30,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,27; -20,06</t>
+          <t>-65,97; -21,94</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-84,12; -32,2</t>
+          <t>-81,53; -31,19</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,8; -25,62</t>
+          <t>-74,81; -27,11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-55,59; -21,66</t>
+          <t>-54,68; -20,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-61,13; -27,09</t>
+          <t>-58,86; -26,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-70,06; -35,72</t>
+          <t>-68,14; -36,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-39,95; -27,58</t>
+          <t>-40,9; -27,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -33,01</t>
+          <t>-47,05; -33,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -25,94</t>
+          <t>-51,43; -24,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -30,78</t>
+          <t>-44,18; -31,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-53,74; -38,47</t>
+          <t>-53,23; -38,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-48,37; -34,12</t>
+          <t>-48,91; -34,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -31,14</t>
+          <t>-40,03; -30,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -37,37</t>
+          <t>-47,72; -37,32</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-47,17; -31,11</t>
+          <t>-47,4; -31,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,95; -27,58</t>
+          <t>-40,9; -27,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -33,01</t>
+          <t>-47,05; -33,07</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -25,94</t>
+          <t>-51,43; -24,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -30,78</t>
+          <t>-44,18; -31,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,74; -38,47</t>
+          <t>-53,23; -38,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,37; -34,12</t>
+          <t>-48,91; -34,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -31,14</t>
+          <t>-40,03; -30,6</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -37,37</t>
+          <t>-47,72; -37,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-47,17; -31,11</t>
+          <t>-47,4; -31,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-55,43; -19,11</t>
+          <t>-54,38; -20,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-71,78; -30,55</t>
+          <t>-74,59; -33,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-65,83; -34,34</t>
+          <t>-65,84; -33,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -16,48</t>
+          <t>-49,57; -15,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,49; -28,29</t>
+          <t>-66,51; -26,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,54; -26,86</t>
+          <t>-60,37; -26,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,29; -21,81</t>
+          <t>-44,89; -21,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -36,84</t>
+          <t>-63,93; -35,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-59,26; -34,96</t>
+          <t>-58,06; -34,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,43; -19,11</t>
+          <t>-54,38; -20,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,78; -30,55</t>
+          <t>-74,59; -33,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,83; -34,34</t>
+          <t>-65,84; -33,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,54; -16,48</t>
+          <t>-49,57; -15,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,49; -28,29</t>
+          <t>-66,51; -26,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,54; -26,86</t>
+          <t>-60,37; -26,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,29; -21,81</t>
+          <t>-44,89; -21,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,74; -36,84</t>
+          <t>-63,93; -35,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,26; -34,96</t>
+          <t>-58,06; -34,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,27; -11,2</t>
+          <t>-42,9; -11,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -15,94</t>
+          <t>-60,32; -15,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -21,24</t>
+          <t>-53,59; -20,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-64,98; -17,34</t>
+          <t>-63,32; -18,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,37; -18,17</t>
+          <t>-55,49; -19,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,93; -15,03</t>
+          <t>-49,25; -15,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,53; -17,94</t>
+          <t>-42,46; -18,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,29; -21,26</t>
+          <t>-49,98; -21,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -21,95</t>
+          <t>-45,96; -21,87</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,27; -11,2</t>
+          <t>-42,9; -11,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -15,94</t>
+          <t>-60,32; -15,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,66; -21,24</t>
+          <t>-53,59; -20,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,98; -17,34</t>
+          <t>-63,32; -18,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; -18,17</t>
+          <t>-55,49; -19,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,93; -15,03</t>
+          <t>-49,25; -15,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,53; -17,94</t>
+          <t>-42,46; -18,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,29; -21,26</t>
+          <t>-49,98; -21,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -21,95</t>
+          <t>-45,96; -21,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -5,46</t>
+          <t>-43,06; -5,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-57,44; -8,09</t>
+          <t>-55,34; -8,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-68,83; -21,02</t>
+          <t>-70,32; -22,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-45,63; -5,91</t>
+          <t>-46,48; -5,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -23,51</t>
+          <t>-71,96; -19,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,39; -28,91</t>
+          <t>-70,99; -27,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -8,98</t>
+          <t>-37,97; -9,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,48; -19,74</t>
+          <t>-57,34; -21,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -32,21</t>
+          <t>-65,69; -33,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,76; -5,46</t>
+          <t>-43,06; -5,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,44; -8,09</t>
+          <t>-55,34; -8,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,83; -21,02</t>
+          <t>-70,32; -22,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; -5,91</t>
+          <t>-46,48; -5,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -23,51</t>
+          <t>-71,96; -19,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,39; -28,91</t>
+          <t>-70,99; -27,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,74; -8,98</t>
+          <t>-37,97; -9,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,48; -19,74</t>
+          <t>-57,34; -21,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -32,21</t>
+          <t>-65,69; -33,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-54,13; -30,94</t>
+          <t>-54,79; -31,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-51,32; -28,68</t>
+          <t>-51,81; -27,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -12,38</t>
+          <t>-61,24; -11,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-54,88; -33,61</t>
+          <t>-54,67; -33,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-68,01; -41,56</t>
+          <t>-69,08; -40,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-53,86; -27,74</t>
+          <t>-54,45; -26,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -34,82</t>
+          <t>-51,38; -35,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,83; -37,73</t>
+          <t>-54,98; -37,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-51,07; -18,04</t>
+          <t>-51,63; -16,76</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,13; -30,94</t>
+          <t>-54,79; -31,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,32; -28,68</t>
+          <t>-51,81; -27,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,31; -12,38</t>
+          <t>-61,24; -11,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,88; -33,61</t>
+          <t>-54,67; -33,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-68,01; -41,56</t>
+          <t>-69,08; -40,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,86; -27,74</t>
+          <t>-54,45; -26,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,63; -34,82</t>
+          <t>-51,38; -35,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,83; -37,73</t>
+          <t>-54,98; -37,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,07; -18,04</t>
+          <t>-51,63; -16,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-48,33; -19,5</t>
+          <t>-48,25; -18,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-59,02; -26,12</t>
+          <t>-58,04; -26,98</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-59,47; -29,61</t>
+          <t>-61,78; -30,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-46,77; -18,91</t>
+          <t>-47,59; -18,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -19,6</t>
+          <t>-50,9; -20,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -29,48</t>
+          <t>-58,28; -28,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -22,68</t>
+          <t>-44,84; -23,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -26,62</t>
+          <t>-49,16; -26,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-54,11; -33,06</t>
+          <t>-56,36; -34,35</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,33; -19,5</t>
+          <t>-48,25; -18,67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,02; -26,12</t>
+          <t>-58,04; -26,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-59,47; -29,61</t>
+          <t>-61,78; -30,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,77; -18,91</t>
+          <t>-47,59; -18,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -19,6</t>
+          <t>-50,9; -20,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,82; -29,48</t>
+          <t>-58,28; -28,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-43,99; -22,68</t>
+          <t>-44,84; -23,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -26,62</t>
+          <t>-49,16; -26,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,11; -33,06</t>
+          <t>-56,36; -34,35</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-69,12; -9,36</t>
+          <t>-68,99; -9,27</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-53,51; -11,76</t>
+          <t>-54,55; -13,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -30,39</t>
+          <t>-78,2; -32,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -21,94</t>
+          <t>-63,64; -21,38</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-81,53; -31,19</t>
+          <t>-80,9; -31,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-74,81; -27,11</t>
+          <t>-73,64; -26,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-54,68; -20,69</t>
+          <t>-54,43; -20,4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-58,86; -26,0</t>
+          <t>-60,73; -25,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-68,14; -36,41</t>
+          <t>-68,24; -36,75</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-69,12; -9,36</t>
+          <t>-68,99; -9,27</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-53,51; -11,76</t>
+          <t>-54,55; -13,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -30,39</t>
+          <t>-78,2; -32,4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-65,97; -21,94</t>
+          <t>-63,64; -21,38</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,53; -31,19</t>
+          <t>-80,9; -31,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,81; -27,11</t>
+          <t>-73,64; -26,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-54,68; -20,69</t>
+          <t>-54,43; -20,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-58,86; -26,0</t>
+          <t>-60,73; -25,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,14; -36,41</t>
+          <t>-68,24; -36,75</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-40,9; -27,6</t>
+          <t>-40,16; -27,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -33,07</t>
+          <t>-46,69; -32,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-51,43; -24,24</t>
+          <t>-51,37; -24,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -31,48</t>
+          <t>-43,56; -30,64</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-53,23; -38,07</t>
+          <t>-53,28; -38,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-48,91; -34,96</t>
+          <t>-48,28; -34,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-40,03; -30,6</t>
+          <t>-40,15; -30,64</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -37,32</t>
+          <t>-47,52; -36,95</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -31,93</t>
+          <t>-47,42; -30,82</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,9; -27,6</t>
+          <t>-40,16; -27,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -33,07</t>
+          <t>-46,69; -32,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,43; -24,24</t>
+          <t>-51,37; -24,97</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -31,48</t>
+          <t>-43,56; -30,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,23; -38,07</t>
+          <t>-53,28; -38,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,91; -34,96</t>
+          <t>-48,28; -34,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,03; -30,6</t>
+          <t>-40,15; -30,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -37,32</t>
+          <t>-47,52; -36,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-47,4; -31,93</t>
+          <t>-47,42; -30,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumieron medicamentos para  el catarro, gripe, garganta, bronquios</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-31,18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-47,25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-44,55</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-35,06</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-54,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-50,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-31,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-47,25</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-43,35</t>
+          <t>-49,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-46,3</t>
+          <t>-46,63</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -20,27</t>
+          <t>-49,7; -16,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-74,59; -33,54</t>
+          <t>-66,21; -27,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -33,22</t>
+          <t>-65,13; -30,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -15,51</t>
+          <t>-53,14; -18,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,51; -26,97</t>
+          <t>-73,69; -32,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,37; -26,46</t>
+          <t>-63,98; -33,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -21,85</t>
+          <t>-45,57; -21,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -35,06</t>
+          <t>-63,15; -36,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-58,06; -34,7</t>
+          <t>-58,52; -35,57</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-31,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-47,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-44,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-35,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-54,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-50,02%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-31,18%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-47,25%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,35%</t>
+          <t>-49,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-46,3%</t>
+          <t>-46,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -20,27</t>
+          <t>-49,7; -16,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,59; -33,54</t>
+          <t>-66,21; -27,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -33,22</t>
+          <t>-65,13; -30,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -15,51</t>
+          <t>-53,14; -18,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,51; -26,97</t>
+          <t>-73,69; -32,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,37; -26,46</t>
+          <t>-63,98; -33,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -21,85</t>
+          <t>-45,57; -21,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -35,06</t>
+          <t>-63,15; -36,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,06; -34,7</t>
+          <t>-58,52; -35,57</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-39,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-34,72</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-29,72</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-24,74</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-35,75</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-35,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-39,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-34,72</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-29,84</t>
+          <t>-36,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-32,8</t>
+          <t>-33,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -11,95</t>
+          <t>-64,3; -17,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-60,32; -15,7</t>
+          <t>-52,97; -17,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-53,59; -20,24</t>
+          <t>-49,18; -15,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-63,32; -18,0</t>
+          <t>-41,76; -12,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,49; -19,02</t>
+          <t>-58,92; -15,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,25; -15,3</t>
+          <t>-53,16; -20,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,46; -18,61</t>
+          <t>-42,82; -18,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -21,63</t>
+          <t>-48,79; -21,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -21,87</t>
+          <t>-47,03; -21,81</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-39,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-34,72%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-29,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-24,74%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-35,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-35,77%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-39,27%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-34,72%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-29,84%</t>
+          <t>-36,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-32,8%</t>
+          <t>-33,29%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-42,9; -11,95</t>
+          <t>-64,3; -17,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,32; -15,7</t>
+          <t>-52,97; -17,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,59; -20,24</t>
+          <t>-49,18; -15,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,32; -18,0</t>
+          <t>-41,76; -12,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,49; -19,02</t>
+          <t>-58,92; -15,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,25; -15,3</t>
+          <t>-53,16; -20,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,46; -18,61</t>
+          <t>-42,82; -18,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,98; -21,63</t>
+          <t>-48,79; -21,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,96; -21,87</t>
+          <t>-47,03; -21,81</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-22,88</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-46,39</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-47,62</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-17,92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-26,97</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-46,39</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-22,88</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-46,39</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-50,99</t>
+          <t>-50,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-49,35</t>
+          <t>-48,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-43,06; -5,39</t>
+          <t>-46,16; -5,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-55,34; -8,15</t>
+          <t>-71,52; -18,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -22,79</t>
+          <t>-70,03; -26,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -5,96</t>
+          <t>-42,35; -5,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -19,79</t>
+          <t>-57,05; -6,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,99; -27,48</t>
+          <t>-75,38; -25,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,97; -9,11</t>
+          <t>-37,14; -9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -21,07</t>
+          <t>-56,24; -21,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -33,97</t>
+          <t>-66,4; -33,25</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-22,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-46,39%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-47,62%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-17,92%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-26,97%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-46,39%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-22,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-46,39%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,99%</t>
+          <t>-50,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-49,35%</t>
+          <t>-48,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,06; -5,39</t>
+          <t>-46,16; -5,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,34; -8,15</t>
+          <t>-71,52; -18,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -22,79</t>
+          <t>-70,03; -26,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,48; -5,96</t>
+          <t>-42,35; -5,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,96; -19,79</t>
+          <t>-57,05; -6,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-70,99; -27,48</t>
+          <t>-75,38; -25,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,97; -9,11</t>
+          <t>-37,14; -9,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,34; -21,07</t>
+          <t>-56,24; -21,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,69; -33,97</t>
+          <t>-66,4; -33,25</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-43,61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-54,85</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-38,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-42,67</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-39,49</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-35,94</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-43,61</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-54,85</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-38,15</t>
+          <t>-44,14</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-36,87</t>
+          <t>-40,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-54,79; -31,73</t>
+          <t>-54,29; -32,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-51,81; -27,87</t>
+          <t>-68,06; -40,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -11,24</t>
+          <t>-55,76; -27,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-54,67; -33,41</t>
+          <t>-54,87; -32,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -40,81</t>
+          <t>-51,16; -28,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-54,45; -26,47</t>
+          <t>-57,36; -30,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -35,4</t>
+          <t>-51,26; -35,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,98; -37,1</t>
+          <t>-53,9; -36,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-51,63; -16,76</t>
+          <t>-51,2; -32,67</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-43,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-54,85%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-38,08%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-42,67%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-39,49%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-35,94%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-43,61%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-54,85%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-38,15%</t>
+          <t>-44,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,87%</t>
+          <t>-40,87%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,79; -31,73</t>
+          <t>-54,29; -32,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,81; -27,87</t>
+          <t>-68,06; -40,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-61,24; -11,24</t>
+          <t>-55,76; -27,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,67; -33,41</t>
+          <t>-54,87; -32,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -40,81</t>
+          <t>-51,16; -28,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,45; -26,47</t>
+          <t>-57,36; -30,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -35,4</t>
+          <t>-51,26; -35,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,98; -37,1</t>
+          <t>-53,9; -36,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,63; -16,76</t>
+          <t>-51,2; -32,67</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-32,02</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-33,52</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-41,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-32,55</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-41,81</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-44,64</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-32,02</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-33,52</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-42,92</t>
+          <t>-44,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-43,69</t>
+          <t>-42,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -18,67</t>
+          <t>-51,05; -20,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-58,04; -26,98</t>
+          <t>-50,54; -19,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-61,78; -30,21</t>
+          <t>-56,38; -27,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -18,45</t>
+          <t>-48,89; -20,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,9; -20,07</t>
+          <t>-57,9; -24,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-58,28; -28,93</t>
+          <t>-59,59; -29,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-44,84; -23,34</t>
+          <t>-42,91; -23,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-49,16; -26,79</t>
+          <t>-48,59; -25,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-56,36; -34,35</t>
+          <t>-52,27; -31,94</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-32,02%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-33,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-41,35%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-32,55%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-41,81%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-44,64%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-32,02%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-33,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-42,92%</t>
+          <t>-44,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-43,69%</t>
+          <t>-42,73%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,25; -18,67</t>
+          <t>-51,05; -20,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,04; -26,98</t>
+          <t>-50,54; -19,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,78; -30,21</t>
+          <t>-56,38; -27,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,59; -18,45</t>
+          <t>-48,89; -20,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,9; -20,07</t>
+          <t>-57,9; -24,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-58,28; -28,93</t>
+          <t>-59,59; -29,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,84; -23,34</t>
+          <t>-42,91; -23,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,16; -26,79</t>
+          <t>-48,59; -25,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,36; -34,35</t>
+          <t>-52,27; -31,94</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-40,94</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-60,04</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-51,68</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-29,87</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-30,44</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-55,65</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-40,94</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-60,04</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-50,95</t>
+          <t>-56,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-53,03</t>
+          <t>-53,74</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-68,99; -9,27</t>
+          <t>-64,27; -20,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-54,55; -13,15</t>
+          <t>-84,12; -32,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-78,2; -32,4</t>
+          <t>-74,67; -27,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-63,64; -21,38</t>
+          <t>-70,06; -9,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-80,9; -31,23</t>
+          <t>-55,19; -13,59</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-73,64; -26,78</t>
+          <t>-77,97; -31,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -20,4</t>
+          <t>-55,59; -21,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -25,45</t>
+          <t>-61,13; -27,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-68,24; -36,75</t>
+          <t>-69,92; -36,07</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-40,94%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-60,04%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-51,68%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-29,87%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-30,44%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-55,65%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-40,94%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-60,04%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-50,95%</t>
+          <t>-56,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-53,03%</t>
+          <t>-53,74%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-68,99; -9,27</t>
+          <t>-64,27; -20,06</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-54,55; -13,15</t>
+          <t>-84,12; -32,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,2; -32,4</t>
+          <t>-74,67; -27,04</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,64; -21,38</t>
+          <t>-70,06; -9,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,9; -31,23</t>
+          <t>-55,19; -13,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,64; -26,78</t>
+          <t>-77,97; -31,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-54,43; -20,4</t>
+          <t>-55,59; -21,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -25,45</t>
+          <t>-61,13; -27,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,24; -36,75</t>
+          <t>-69,92; -36,07</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-37,19</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-45,43</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-40,77</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-33,77</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-39,64</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-41,29</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-37,19</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-45,43</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-41,26</t>
+          <t>-45,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-41,28</t>
+          <t>-42,88</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -27,16</t>
+          <t>-43,99; -30,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-46,69; -32,65</t>
+          <t>-53,74; -38,47</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-51,37; -24,97</t>
+          <t>-48,4; -33,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -30,64</t>
+          <t>-39,95; -27,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-53,28; -38,07</t>
+          <t>-47,05; -33,01</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-48,28; -34,44</t>
+          <t>-52,67; -38,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -30,64</t>
+          <t>-40,25; -31,14</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-47,52; -36,95</t>
+          <t>-47,53; -37,37</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-47,42; -30,82</t>
+          <t>-47,77; -38,14</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-37,19%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-45,43%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-40,77%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-33,77%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-39,64%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-41,29%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-37,19%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-45,43%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-41,26%</t>
+          <t>-45,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-41,28%</t>
+          <t>-42,88%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -27,16</t>
+          <t>-43,99; -30,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,69; -32,65</t>
+          <t>-53,74; -38,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,37; -24,97</t>
+          <t>-48,4; -33,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -30,64</t>
+          <t>-39,95; -27,58</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,28; -38,07</t>
+          <t>-47,05; -33,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-48,28; -34,44</t>
+          <t>-52,67; -38,94</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -30,64</t>
+          <t>-40,25; -31,14</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,52; -36,95</t>
+          <t>-47,53; -37,37</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-47,42; -30,82</t>
+          <t>-47,77; -38,14</t>
         </is>
       </c>
     </row>
